--- a/Data/Results/System/Trip_Log_Reconciliation.xlsx
+++ b/Data/Results/System/Trip_Log_Reconciliation.xlsx
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Run Summary'!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'One-to-One Match Map'!$A$1:$W$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ready Verified Trips'!$A$1:$BN$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'One-to-One Match Map'!$A$1:$W$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ready Verified Trips'!$A$1:$BN$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Data Check Required'!$A$1:$BN$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Unmatched Indexed Files'!$A$1:$AU$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Unmatched Log Rows'!$A$1:$A$1</definedName>
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29T11:12:41</t>
+          <t>2026-10-06T23:14:18</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W35"/>
+  <dimension ref="A1:W41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -761,16 +761,16 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>trip_14d8756c6ad1716d</t>
+          <t>trip_f1948b8b1dd14218</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>log_1449b7cfda9ff2</t>
+          <t>log_117f2e1c26ca9e</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>135.149</v>
+        <v>144.746</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
@@ -780,20 +780,20 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>chennai &gt; pondicherry</t>
+          <t>madiwala &gt; maduravoyal</t>
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>46222.47083333333</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>46222.6375</v>
+        <v>46299.16180555556</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>9.25</v>
+        <v>0.033</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>700.033</v>
+        <v>18.25</v>
       </c>
       <c r="K2" s="2" t="b">
         <v>0</v>
@@ -802,7 +802,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>135.149</v>
+        <v>144.746</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
@@ -811,12 +811,12 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>chennai_to_pondi_diesel_INTERCITY.xlsx</t>
+          <t>madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>19-07-2026\chennai_to_pondi_diesel_INTERCITY.xlsx</t>
+          <t>03-10-2026\madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -825,45 +825,45 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="S2" s="5" t="n">
-        <v>46222</v>
+        <v>46298</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Madiwala</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Maduravoyal</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>03:18</t>
+          <t>03:53 (+1 day)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>trip_0b4db0b9bf4232de</t>
+          <t>trip_13cc5a5f3743a171</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>log_170a15d3292e9d</t>
+          <t>log_12f913058881aa</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>144.733</v>
+        <v>143.793</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>46283.71527777778</v>
+        <v>46297.97847222222</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>46284.01597222222</v>
+        <v>46298.20277777778</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4.9</v>
+        <v>58.867</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>14.317</v>
+        <v>28.05</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>144.733</v>
+        <v>143.793</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>18-09-2026\maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+          <t>02-10-2026\maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>46283</v>
+        <v>46297</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -935,28 +935,28 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>17:10:00</t>
+          <t>23:29:00</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>00:23 (+1 day)</t>
+          <t>04:52 (+1 day)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>trip_98d159ea76b0664d</t>
+          <t>trip_14d8756c6ad1716d</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>log_18201ae2b8acd3</t>
+          <t>log_1449b7cfda9ff2</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>141.716</v>
+        <v>135.149</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
@@ -966,20 +966,20 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>avrroundanasalem &gt; avrroundanasalem &gt; silkboard</t>
+          <t>chennai &gt; pondicherry</t>
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>46232.47430555556</v>
+        <v>46222.47083333333</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>46232.64305555556</v>
+        <v>46222.6375</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.717</v>
+        <v>9.25</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>19.717</v>
+        <v>700.033</v>
       </c>
       <c r="K4" s="2" t="b">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>1</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>141.716</v>
+        <v>135.149</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
@@ -997,59 +997,59 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>avr_roundana(salem)_to_silkboard_ev_INTERCITY.xlsx</t>
+          <t>chennai_to_pondi_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>29-07-2026\avr_roundana(salem)_to_silkboard_ev_INTERCITY.xlsx</t>
+          <t>19-07-2026\chennai_to_pondi_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="R4" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>46232</v>
+        <v>46222</v>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>AVR Roundana (Salem)</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>Silk Board</t>
+          <t>Pondicherry</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11:23:00</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15:26:00</t>
+          <t>03:18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>trip_0d42786207d3e25b</t>
+          <t>trip_0b4db0b9bf4232de</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>log_185be5be166583</t>
+          <t>log_170a15d3292e9d</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>144.284</v>
+        <v>144.733</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
@@ -1059,20 +1059,20 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>chennai &gt; bangalore</t>
+          <t>maduravoyal &gt; madiwala</t>
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>46269.97569444445</v>
+        <v>46283.71527777778</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>46270.23958333334</v>
+        <v>46284.01597222222</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>31.133</v>
+        <v>4.9</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>20.383</v>
+        <v>14.317</v>
       </c>
       <c r="K5" s="2" t="b">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>144.284</v>
+        <v>144.733</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>chennai_to_bangalore_diesel_intercity.xlsx</t>
+          <t>maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>04-09-2026\chennai_to_bangalore_diesel_intercity.xlsx</t>
+          <t>18-09-2026\maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1104,45 +1104,45 @@
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>46269</v>
+        <v>46283</v>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Maduravoyal</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Madiwala</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23:25:00</t>
+          <t>17:10:00</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>05:45 (+1 day)</t>
+          <t>00:23 (+1 day)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>trip_16d184b684a03a18</t>
+          <t>trip_98d159ea76b0664d</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>log_19315da55d829f</t>
+          <t>log_18201ae2b8acd3</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>133.988</v>
+        <v>141.716</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
@@ -1152,20 +1152,20 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>pondicherry &gt; chennai</t>
+          <t>avrroundanasalem &gt; avrroundanasalem &gt; silkboard</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>46221.08333333334</v>
+        <v>46232.47430555556</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>46221.28888888889</v>
+        <v>46232.64305555556</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>120</v>
+        <v>0.717</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>672.833</v>
+        <v>19.717</v>
       </c>
       <c r="K6" s="2" t="b">
         <v>0</v>
@@ -1174,7 +1174,7 @@
         <v>1</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>133.988</v>
+        <v>141.716</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>pondi_to_chennai_ev_INTERCITY.xlsx</t>
+          <t>avr_roundana(salem)_to_silkboard_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>18-07-2026\pondi_to_chennai_ev_INTERCITY.xlsx</t>
+          <t>29-07-2026\avr_roundana(salem)_to_silkboard_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1197,45 +1197,45 @@
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>46221</v>
+        <v>46232</v>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>AVR Roundana (Salem)</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Silk Board</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>11:23:00</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>06:56</t>
+          <t>15:26:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>trip_8156987b197bce50</t>
+          <t>trip_0d42786207d3e25b</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>log_1a942a68c22847</t>
+          <t>log_185be5be166583</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>144.907</v>
+        <v>144.284</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>madiwala &gt; maduravoyal</t>
+          <t>chennai &gt; bangalore</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>46277.94444444445</v>
+        <v>46269.97569444445</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>46278.25486111111</v>
+        <v>46270.23958333334</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.517</v>
+        <v>31.133</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>6.183</v>
+        <v>20.383</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>144.907</v>
+        <v>144.284</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
@@ -1276,59 +1276,59 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+          <t>chennai_to_bangalore_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>12-09-2026\madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+          <t>04-09-2026\chennai_to_bangalore_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="R7" s="2" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>46277</v>
+        <v>46269</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>Madiwala</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>Maduravoyal</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22:40:00</t>
+          <t>23:25:00</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>06:07 (+1 day)</t>
+          <t>05:45 (+1 day)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>trip_9d994ab4d25d3553</t>
+          <t>trip_16d184b684a03a18</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>log_1ed12feb499e18</t>
+          <t>log_19315da55d829f</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>141.833</v>
+        <v>133.988</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
@@ -1342,16 +1342,16 @@
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>46221.67916666667</v>
+        <v>46221.08333333334</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>46221.84305555555</v>
+        <v>46221.28888888889</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2.017</v>
+        <v>120</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>226</v>
+        <v>672.833</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>0</v>
@@ -1360,7 +1360,7 @@
         <v>1</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>141.833</v>
+        <v>133.988</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>pondi_to_chennai_diesel_INTERCITY.xlsx</t>
+          <t>pondi_to_chennai_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>18-07-2026\pondi_to_chennai_diesel_INTERCITY.xlsx</t>
+          <t>18-07-2026\pondi_to_chennai_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="R8" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S8" s="5" t="n">
         <v>46221</v>
@@ -1400,28 +1400,28 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>06:56</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>trip_68c3fb97cf40032c</t>
+          <t>trip_8156987b197bce50</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>log_27b7d635759d0b</t>
+          <t>log_1a942a68c22847</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>144.981</v>
+        <v>144.907</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
@@ -1431,20 +1431,20 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>chennai &gt; pondicherry</t>
+          <t>madiwala &gt; maduravoyal</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>46290.56041666667</v>
+        <v>46277.94444444445</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>46290.77708333333</v>
+        <v>46278.25486111111</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.467</v>
+        <v>0.517</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.917</v>
+        <v>6.183</v>
       </c>
       <c r="K9" s="2" t="b">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>144.981</v>
+        <v>144.907</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>chennai_to_pondicherry_ev_intercity.xlsx</t>
+          <t>madiwala_to_maduravoyal_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>25-09-2026\chennai_to_pondicherry_ev_intercity.xlsx</t>
+          <t>12-09-2026\madiwala_to_maduravoyal_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1476,45 +1476,45 @@
         </is>
       </c>
       <c r="R9" s="2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>46290</v>
+        <v>46277</v>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Madiwala</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Maduravoyal</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13:27:00</t>
+          <t>22:40:00</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18:39:00</t>
+          <t>06:07 (+1 day)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>trip_6bcc4292a35a75d5</t>
+          <t>trip_9d994ab4d25d3553</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>log_3c76ff67789df0</t>
+          <t>log_1ed12feb499e18</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>144.219</v>
+        <v>141.833</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
@@ -1524,20 +1524,20 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>silkboard &gt; maduravoyal</t>
+          <t>pondicherry &gt; chennai</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>46232.95625</v>
+        <v>46221.67916666667</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>46233.18888888889</v>
+        <v>46221.84305555555</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>37.067</v>
+        <v>2.017</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>19.15</v>
+        <v>226</v>
       </c>
       <c r="K10" s="2" t="b">
         <v>0</v>
@@ -1546,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>144.219</v>
+        <v>141.833</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>silkboard_to_maduravoyal_diesel_INTERCITY.xlsx</t>
+          <t>pondi_to_chennai_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>29-07-2026\silkboard_to_maduravoyal_diesel_INTERCITY.xlsx</t>
+          <t>18-07-2026\pondi_to_chennai_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1569,45 +1569,45 @@
         </is>
       </c>
       <c r="R10" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>46232</v>
+        <v>46221</v>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>Silk Board</t>
+          <t>Pondicherry</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>Maduravayol</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22:57:00</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>04:32:00</t>
+          <t>20:14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>trip_71d3df4d8a429e71</t>
+          <t>trip_25c5675923bf855a</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>log_4323f7ccfddbf5</t>
+          <t>log_1fa2f4469203bc</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>144.391</v>
+        <v>144.975</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0</v>
@@ -1617,20 +1617,20 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>maduravoyal &gt; silkboard</t>
+          <t>madiwala &gt; maduravoyal</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>46213.01666666667</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>46213.25694444445</v>
+        <v>46299.20833333334</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>24</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>19.817</v>
+        <v>0.85</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
@@ -1639,7 +1639,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>144.391</v>
+        <v>144.975</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>madhuravoyal_to_silkboard_ev_INTERCITY.xlsx</t>
+          <t>madiwala_to_maduravoyal_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>10-07-2026\madhuravoyal_to_silkboard_ev_INTERCITY.xlsx</t>
+          <t>03-10-2026\madiwala_to_maduravoyal_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1662,45 +1662,45 @@
         </is>
       </c>
       <c r="R11" s="2" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>46213</v>
+        <v>46298</v>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
+          <t>Madiwala</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>Maduravoyal</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>Silk Board</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>00:24</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>05:00 (+1 day)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>trip_fa6bc7146b74fda0</t>
+          <t>trip_68c3fb97cf40032c</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>log_43b0c84a5b047e</t>
+          <t>log_27b7d635759d0b</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>144.692</v>
+        <v>144.981</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0</v>
@@ -1710,20 +1710,20 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>madiwala &gt; maduravoyal</t>
+          <t>chennai &gt; pondicherry</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>46285.50833333333</v>
+        <v>46290.56041666667</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>46285.75347222222</v>
+        <v>46290.77708333333</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.967</v>
+        <v>0.467</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21.2</v>
+        <v>0.917</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>144.692</v>
+        <v>144.981</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -1741,59 +1741,59 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
+          <t>chennai_to_pondicherry_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>20-09-2026\madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
+          <t>25-09-2026\chennai_to_pondicherry_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="R12" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>46285</v>
+        <v>46290</v>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>Madiwala</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>Maduravoyal</t>
+          <t>Pondicherry</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12:12:00</t>
+          <t>13:27:00</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18:05:00</t>
+          <t>18:39:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>trip_3ada1f4458de6612</t>
+          <t>trip_6bcc4292a35a75d5</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>log_46055a674e6435</t>
+          <t>log_3c76ff67789df0</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>144.573</v>
+        <v>144.219</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0</v>
@@ -1803,20 +1803,20 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>maduravoyal &gt; madiwala</t>
+          <t>silkboard &gt; maduravoyal</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>46276.96944444445</v>
+        <v>46232.95625</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>46277.24444444444</v>
+        <v>46233.18888888889</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>37.067</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>29.733</v>
+        <v>19.15</v>
       </c>
       <c r="K13" s="2" t="b">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>144.573</v>
+        <v>144.219</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1834,59 +1834,59 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>maduravoyal_to_madiwala_ev_intercity.xlsx</t>
+          <t>silkboard_to_maduravoyal_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>11-09-2026\maduravoyal_to_madiwala_ev_intercity.xlsx</t>
+          <t>29-07-2026\silkboard_to_maduravoyal_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="R13" s="2" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>46276</v>
+        <v>46232</v>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>Maduravoyal</t>
+          <t>Silk Board</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>Madiwala</t>
+          <t>Maduravayol</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23:16:00</t>
+          <t>22:57:00</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>05:52 (+1 day)</t>
+          <t>04:32:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>trip_e856facc25a4ac93</t>
+          <t>trip_c878323a9bdf7813</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>log_47638edc2c406f</t>
+          <t>log_4058b1efc303e6</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>130.107</v>
+        <v>144.671</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
@@ -1896,20 +1896,20 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>silkboard &gt; avrroundanasalem &gt; avrroundanasalem</t>
+          <t>maduravoyal &gt; madiwala</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>46231.28888888889</v>
+        <v>46297.96388888889</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>46231.46527777778</v>
+        <v>46298.21319444444</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>416</v>
+        <v>0.783</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>440.3</v>
+        <v>22.9</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>130.107</v>
+        <v>144.671</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>silkboard_to_avr_roundana(salem)_ev_INTERCITY.xlsx</t>
+          <t>maduravoyal_to_madiwala_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>28-07-2026\silkboard_to_avr_roundana(salem)_ev_INTERCITY.xlsx</t>
+          <t>02-10-2026\maduravoyal_to_madiwala_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,45 +1941,45 @@
         </is>
       </c>
       <c r="R14" s="2" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>46231</v>
+        <v>46297</v>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>Silk Board</t>
+          <t>Maduravoyal</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>AVR Roundana (Salem)</t>
+          <t>Madiwala</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:56:00</t>
+          <t>23:08:00</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11:10:00</t>
+          <t>05:07 (+1 day)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>trip_dd265c96e0c8309d</t>
+          <t>trip_71d3df4d8a429e71</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>log_4a99e6412740d7</t>
+          <t>log_4323f7ccfddbf5</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>125.634</v>
+        <v>144.391</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0</v>
@@ -1989,20 +1989,20 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>pondicherry &gt; chennai</t>
+          <t>maduravoyal &gt; silkboard</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>46219.58333333334</v>
+        <v>46213.01666666667</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>46219.78680555556</v>
+        <v>46213.25694444445</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>718.817</v>
+        <v>24</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>675.5</v>
+        <v>19.817</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
@@ -2011,7 +2011,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>125.634</v>
+        <v>144.391</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -2020,12 +2020,12 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>pondi_to_chennai_ev_INTERCITY.xlsx</t>
+          <t>madhuravoyal_to_silkboard_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>16-07-2026\pondi_to_chennai_ev_INTERCITY.xlsx</t>
+          <t>10-07-2026\madhuravoyal_to_silkboard_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2034,45 +2034,45 @@
         </is>
       </c>
       <c r="R15" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>46219</v>
+        <v>46213</v>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Maduravoyal</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Silk Board</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:24</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>06:10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>trip_02feefe36bd89388</t>
+          <t>trip_fa6bc7146b74fda0</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>log_5cb7bfc0ba0960</t>
+          <t>log_43b0c84a5b047e</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>125</v>
+        <v>144.692</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
@@ -2082,17 +2082,21 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>chennai &gt; pondicherry</t>
+          <t>madiwala &gt; maduravoyal</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>46218.38888888889</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
+        <v>46285.50833333333</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>46285.75347222222</v>
+      </c>
       <c r="I16" s="2" t="n">
-        <v>560</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
+        <v>0.967</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>21.2</v>
+      </c>
       <c r="K16" s="2" t="b">
         <v>0</v>
       </c>
@@ -2100,7 +2104,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>125</v>
+        <v>144.692</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -2109,55 +2113,59 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>chennai_to_pondi_ev_INTERCITY.xlsx</t>
+          <t>madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>15-07-2026\chennai_to_pondi_ev_INTERCITY.xlsx</t>
+          <t>20-09-2026\madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="R16" s="2" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>46218</v>
+        <v>46285</v>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Madiwala</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Maduravoyal</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr"/>
+          <t>12:12:00</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>18:05:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>trip_46749b9c01c69f66</t>
+          <t>trip_3ada1f4458de6612</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>log_60859e4463804f</t>
+          <t>log_46055a674e6435</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>143.857</v>
+        <v>144.573</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
@@ -2167,20 +2175,20 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>silkboard &gt; maduravoyal</t>
+          <t>maduravoyal &gt; madiwala</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>46271.0125</v>
+        <v>46276.96944444445</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>46271.25138888889</v>
+        <v>46277.24444444444</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.117</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>29.733</v>
       </c>
       <c r="K17" s="2" t="b">
         <v>0</v>
@@ -2189,7 +2197,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>143.857</v>
+        <v>144.573</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -2198,12 +2206,12 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+          <t>maduravoyal_to_madiwala_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>06-09-2026\silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+          <t>11-09-2026\maduravoyal_to_madiwala_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2212,45 +2220,45 @@
         </is>
       </c>
       <c r="R17" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>Silk Board</t>
+          <t>Maduravoyal</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>Maduravoyal</t>
+          <t>Madiwala</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>00:18:00</t>
+          <t>23:16:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>06:02:00</t>
+          <t>05:52 (+1 day)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>trip_68f9b2f1e152392f</t>
+          <t>trip_e856facc25a4ac93</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>log_78cd3ab262788d</t>
+          <t>log_47638edc2c406f</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>144.717</v>
+        <v>130.107</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0</v>
@@ -2260,20 +2268,20 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>silkboard &gt; maduravoyal</t>
+          <t>silkboard &gt; avrroundanasalem &gt; avrroundanasalem</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>46208.35763888889</v>
+        <v>46231.28888888889</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>46208.59722222222</v>
+        <v>46231.46527777778</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.583</v>
+        <v>416</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>19.783</v>
+        <v>440.3</v>
       </c>
       <c r="K18" s="2" t="b">
         <v>0</v>
@@ -2282,7 +2290,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>144.717</v>
+        <v>130.107</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -2291,12 +2299,12 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>silkboard_to_madhuravoyal_ev_INTERCITY.xlsx</t>
+          <t>silkboard_to_avr_roundana(salem)_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>05-07-2026\silkboard_to_madhuravoyal_ev_INTERCITY.xlsx</t>
+          <t>28-07-2026\silkboard_to_avr_roundana(salem)_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2305,10 +2313,10 @@
         </is>
       </c>
       <c r="R18" s="2" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>46208</v>
+        <v>46231</v>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
@@ -2317,33 +2325,33 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>Maduravoyal</t>
+          <t>AVR Roundana (Salem)</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>06:56:00</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:10:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>trip_659ae1911fa4221d</t>
+          <t>trip_dd265c96e0c8309d</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>log_7d0931834be823</t>
+          <t>log_4a99e6412740d7</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>144.958</v>
+        <v>125.634</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0</v>
@@ -2353,20 +2361,20 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>maduravoyal &gt; lalbag</t>
+          <t>pondicherry &gt; chennai</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>46283.75138888889</v>
+        <v>46219.58333333334</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>46284.03125</v>
+        <v>46219.78680555556</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1.5</v>
+        <v>718.817</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.533</v>
+        <v>675.5</v>
       </c>
       <c r="K19" s="2" t="b">
         <v>0</v>
@@ -2375,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>144.958</v>
+        <v>125.634</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -2384,12 +2392,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>maduravoyal_to_lalbag_ev_intercity.xlsx</t>
+          <t>pondi_to_chennai_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>18-09-2026\maduravoyal_to_lalbag_ev_intercity.xlsx</t>
+          <t>16-07-2026\pondi_to_chennai_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2398,45 +2406,45 @@
         </is>
       </c>
       <c r="R19" s="2" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>46283</v>
+        <v>46219</v>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>Maduravoyal</t>
+          <t>Pondicherry</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>Lalbag</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18:02:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>00:45 (+1 day)</t>
+          <t>06:53</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>trip_afcd6bedcb93e8fb</t>
+          <t>trip_02feefe36bd89388</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>log_83dda5bf0eeb8d</t>
+          <t>log_5cb7bfc0ba0960</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>137.287</v>
+        <v>125</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
@@ -2450,17 +2458,13 @@
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>46222.38194444445</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>46222.52430555555</v>
-      </c>
+        <v>46218.38888888889</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>5.3</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="b">
         <v>0</v>
       </c>
@@ -2468,7 +2472,7 @@
         <v>1</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>137.287</v>
+        <v>125</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -2482,7 +2486,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>19-07-2026\chennai_to_pondi_ev_INTERCITY.xlsx</t>
+          <t>15-07-2026\chennai_to_pondi_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2491,10 +2495,10 @@
         </is>
       </c>
       <c r="R20" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>46222</v>
+        <v>46218</v>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
@@ -2508,28 +2512,24 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>trip_1d186832f935e51b</t>
+          <t>trip_46749b9c01c69f66</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>log_8405643e447f49</t>
+          <t>log_60859e4463804f</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>144.124</v>
+        <v>143.857</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0</v>
@@ -2539,20 +2539,20 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>maduravoyal &gt; silkboard</t>
+          <t>silkboard &gt; maduravoyal</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>46234.47013888889</v>
+        <v>46271.0125</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>46235.22708333333</v>
+        <v>46271.25138888889</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>43</v>
+        <v>0.117</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>20.05</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="K21" s="2" t="b">
         <v>0</v>
@@ -2561,7 +2561,7 @@
         <v>1</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>144.124</v>
+        <v>143.857</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -2570,59 +2570,59 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>maduravoyal_to_silkboard_diesel_INTERCITY.xlsx</t>
+          <t>silkboard_to_maduravoyal_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>31-07-2026\maduravoyal_to_silkboard_diesel_INTERCITY.xlsx</t>
+          <t>06-09-2026\silkboard_to_maduravoyal_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="R21" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>46234</v>
+        <v>46271</v>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
+          <t>Silk Board</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
           <t>Maduravoyal</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>Silk Board</t>
-        </is>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23:17:00</t>
+          <t>00:18:00</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>05:27 (01-08-2026)</t>
+          <t>06:02:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>trip_c7fc11871ffe5efd</t>
+          <t>trip_68f9b2f1e152392f</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>log_86218f028dd7d0</t>
+          <t>log_78cd3ab262788d</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>144.732</v>
+        <v>144.717</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
@@ -2632,20 +2632,20 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>maduravoyal &gt; silkboard</t>
+          <t>silkboard &gt; maduravoyal</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>46269.95347222222</v>
+        <v>46208.35763888889</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>46270.35277777778</v>
+        <v>46208.59722222222</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.867</v>
+        <v>0.583</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>18.433</v>
+        <v>19.783</v>
       </c>
       <c r="K22" s="2" t="b">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>144.732</v>
+        <v>144.717</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>maduravoyal_to_silk_board_ev_intercity.xlsx</t>
+          <t>silkboard_to_madhuravoyal_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>04-09-2026\maduravoyal_to_silk_board_ev_intercity.xlsx</t>
+          <t>05-07-2026\silkboard_to_madhuravoyal_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2677,45 +2677,45 @@
         </is>
       </c>
       <c r="R22" s="2" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>46269</v>
+        <v>46208</v>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
+          <t>Silk Board</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>Maduravoyal</t>
         </is>
       </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>Silk Board</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22:53:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>08:28 (+1 day)</t>
+          <t>14:20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>trip_3c71e1051dc32ee3</t>
+          <t>trip_42cecab159306ac4</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>log_862cda94cb0701</t>
+          <t>log_7a83e37e272f23</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>144.913</v>
+        <v>144.376</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0</v>
@@ -2725,20 +2725,20 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>madiwala &gt; maduravoyal</t>
+          <t>chennai &gt; pondicherry</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>46285.47222222222</v>
+        <v>46290.60138888889</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>46285.76180555556</v>
+        <v>46290.80069444444</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6.067</v>
+        <v>1.167</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.2</v>
+        <v>43.75</v>
       </c>
       <c r="K23" s="2" t="b">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>1</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>144.913</v>
+        <v>144.376</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -2756,59 +2756,59 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+          <t>chennai_to_pondicherry_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>20-09-2026\madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+          <t>25-09-2026\chennai_to_pondicherry_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="R23" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>46285</v>
+        <v>46290</v>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>Madiwala</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>Maduravoyal</t>
+          <t>Pondicherry</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11:20:00</t>
+          <t>14:26:00</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18:17 (+1 day)</t>
+          <t>19:13:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>trip_8652f2c6e75d9e83</t>
+          <t>trip_659ae1911fa4221d</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>log_8e12b252255bfd</t>
+          <t>log_7d0931834be823</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>144.941</v>
+        <v>144.958</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
@@ -2818,20 +2818,20 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>silkboard &gt; maduravoyal</t>
+          <t>maduravoyal &gt; lalbag</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>46270.96875</v>
+        <v>46283.75138888889</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>46271.19097222222</v>
+        <v>46284.03125</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.917</v>
+        <v>1.5</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3.367</v>
+        <v>1.533</v>
       </c>
       <c r="K24" s="2" t="b">
         <v>0</v>
@@ -2840,7 +2840,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>144.941</v>
+        <v>144.958</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -2849,59 +2849,59 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>silkboard_to_maduravoyal_diesel_intercity.xlsx</t>
+          <t>maduravoyal_to_lalbag_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>05-09-2026\silkboard_to_maduravoyal_diesel_intercity.xlsx</t>
+          <t>18-09-2026\maduravoyal_to_lalbag_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="R24" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>46270</v>
+        <v>46283</v>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>Silk Board</t>
+          <t>Maduravoyal</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>Maduravoyal</t>
+          <t>Lalbag</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23:15:00</t>
+          <t>18:02:00</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>04:35 (+1 day)</t>
+          <t>00:45 (+1 day)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>trip_96615bbb0bda4efc</t>
+          <t>trip_afcd6bedcb93e8fb</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>log_b02d97e3dc8a0d</t>
+          <t>log_83dda5bf0eeb8d</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>133.734</v>
+        <v>137.287</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0</v>
@@ -2911,20 +2911,20 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>pondicherry &gt; chennai</t>
+          <t>chennai &gt; pondicherry</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>46223.08680555555</v>
+        <v>46222.38194444445</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>46223.26944444444</v>
+        <v>46222.52430555555</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>125</v>
+        <v>550</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>686.117</v>
+        <v>5.3</v>
       </c>
       <c r="K25" s="2" t="b">
         <v>0</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>133.734</v>
+        <v>137.287</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>pondi_to_chennai _ev_INTERCITY.xlsx</t>
+          <t>chennai_to_pondi_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>20-07-2026\pondi_to_chennai _ev_INTERCITY.xlsx</t>
+          <t>19-07-2026\chennai_to_pondi_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -2956,45 +2956,45 @@
         </is>
       </c>
       <c r="R25" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>46223</v>
+        <v>46222</v>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>Pondicherry</t>
         </is>
       </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>02:05</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>12:35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>trip_4bad1d9396432966</t>
+          <t>trip_1d186832f935e51b</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>log_b9357b65d50b28</t>
+          <t>log_8405643e447f49</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>128.889</v>
+        <v>144.124</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0</v>
@@ -3004,20 +3004,20 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>chennai &gt; pondicherry</t>
+          <t>maduravoyal &gt; silkboard</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>46220.31736111111</v>
+        <v>46234.47013888889</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>46220.48819444444</v>
+        <v>46235.22708333333</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>457</v>
+        <v>43</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>703</v>
+        <v>20.05</v>
       </c>
       <c r="K26" s="2" t="b">
         <v>0</v>
@@ -3026,7 +3026,7 @@
         <v>1</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>128.889</v>
+        <v>144.124</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -3035,59 +3035,59 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>chennai_to_pondi_ev_INTERCITY.xlsx</t>
+          <t>maduravoyal_to_silkboard_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>17-07-2026\chennai_to_pondi_ev_INTERCITY.xlsx</t>
+          <t>31-07-2026\maduravoyal_to_silkboard_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="R26" s="2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Maduravoyal</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Silk Board</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>23:17:00</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>05:27 (01-08-2026)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>trip_94455ac95468fa9e</t>
+          <t>trip_c7fc11871ffe5efd</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>log_baab598cc0961a</t>
+          <t>log_86218f028dd7d0</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>144.18</v>
+        <v>144.732</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0</v>
@@ -3097,20 +3097,20 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>madiwala &gt; maduravoyal</t>
+          <t>maduravoyal &gt; silkboard</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>46277.96597222222</v>
+        <v>46269.95347222222</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>46278.19722222222</v>
+        <v>46270.35277777778</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>37.617</v>
+        <v>0.867</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>21.45</v>
+        <v>18.433</v>
       </c>
       <c r="K27" s="2" t="b">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>1</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>144.18</v>
+        <v>144.732</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -3128,59 +3128,59 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
+          <t>maduravoyal_to_silk_board_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>12-09-2026\madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
+          <t>04-09-2026\maduravoyal_to_silk_board_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="R27" s="2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>46277</v>
+        <v>46269</v>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>Madiwala</t>
+          <t>Maduravoyal</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>Maduravoyal</t>
+          <t>Silk Board</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>23:11:00</t>
+          <t>22:53:00</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>04:44 (+1 day)</t>
+          <t>08:28 (+1 day)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>trip_07f23f699f56d574</t>
+          <t>trip_8652f2c6e75d9e83</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>log_bcde7a9312a413</t>
+          <t>log_8e12b252255bfd</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>144.669</v>
+        <v>144.941</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0</v>
@@ -3194,16 +3194,16 @@
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>46223.49583333333</v>
+        <v>46270.96875</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>46223.74861111111</v>
+        <v>46271.19097222222</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6</v>
+        <v>0.917</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>17.8</v>
+        <v>3.367</v>
       </c>
       <c r="K28" s="2" t="b">
         <v>0</v>
@@ -3212,7 +3212,7 @@
         <v>1</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>144.669</v>
+        <v>144.941</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -3221,24 +3221,24 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>silkboard_to_maduravoyal_ev_INTERCITY.xlsx</t>
+          <t>silkboard_to_maduravoyal_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>20-07-2026\silkboard_to_maduravoyal_ev_INTERCITY.xlsx</t>
+          <t>05-09-2026\silkboard_to_maduravoyal_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="R28" s="2" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>46223</v>
+        <v>46270</v>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
@@ -3252,28 +3252,28 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>23:15:00</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>04:35 (+1 day)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>trip_0e87f413df33f4c0</t>
+          <t>trip_3c71e1051dc32ee3</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>log_cf162b454c984b</t>
+          <t>log_95966633d8fcec</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>144.974</v>
+        <v>144.913</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0</v>
@@ -3283,20 +3283,20 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>pondicherry &gt; chennai</t>
+          <t>madiwala &gt; maduravoyal</t>
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>46291.6</v>
+        <v>46285.47222222222</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>46291.78958333333</v>
+        <v>46285.76180555556</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.967</v>
+        <v>6.067</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.917</v>
+        <v>0.2</v>
       </c>
       <c r="K29" s="2" t="b">
         <v>0</v>
@@ -3305,7 +3305,7 @@
         <v>1</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>144.974</v>
+        <v>144.913</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -3314,12 +3314,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>pondicherry_to_chennai_ev_intercity.xlsx</t>
+          <t>madiwala_to_maduravoyal_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>26-09-2026\pondicherry_to_chennai_ev_intercity.xlsx</t>
+          <t>20-09-2026\madiwala_to_maduravoyal_ev_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3328,45 +3328,45 @@
         </is>
       </c>
       <c r="R29" s="2" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Madiwala</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Maduravoyal</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>11:20:00</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18:57:00</t>
+          <t>18:17:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>trip_6088a97c1b8893d7</t>
+          <t>trip_efd3430444a3f8eb</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>log_d0035ab1754ec5</t>
+          <t>log_aba8d06ef2bf51</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>127.749</v>
+        <v>144.841</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0</v>
@@ -3380,16 +3380,16 @@
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>46219.6875</v>
+        <v>46291.67708333334</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>46219.86805555555</v>
+        <v>46291.88194444445</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>712.1</v>
+        <v>3.033</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>530</v>
+        <v>8.382999999999999</v>
       </c>
       <c r="K30" s="2" t="b">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>1</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>127.749</v>
+        <v>144.841</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>pondi_to_chennai_diesel_INTERCITY.xlsx</t>
+          <t>pondicherry_to_chennai_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>16-07-2026\pondi_to_chennai_diesel_INTERCITY.xlsx</t>
+          <t>26-09-2026\pondicherry_to_chennai_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="R30" s="2" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>46219</v>
+        <v>46291</v>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
@@ -3438,28 +3438,28 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>21:10:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>trip_e27cf5973e77ff0f</t>
+          <t>trip_96615bbb0bda4efc</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>log_d48233712f4cfc</t>
+          <t>log_b02d97e3dc8a0d</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>125.654</v>
+        <v>133.734</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0</v>
@@ -3469,20 +3469,20 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>chennai &gt; pondicherry</t>
+          <t>pondicherry &gt; chennai</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>46220.48194444444</v>
+        <v>46223.08680555555</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>46220.64236111111</v>
+        <v>46223.26944444444</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>694</v>
+        <v>125</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>698.933</v>
+        <v>686.117</v>
       </c>
       <c r="K31" s="2" t="b">
         <v>0</v>
@@ -3491,7 +3491,7 @@
         <v>1</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>125.654</v>
+        <v>133.734</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -3500,59 +3500,59 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>chennai_to_pondi_diesel_INTERCITY.xlsx</t>
+          <t>pondi_to_chennai _ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>17-07-2026\chennai_to_pondi_diesel_INTERCITY.xlsx</t>
+          <t>20-07-2026\pondi_to_chennai _ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="R31" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
+          <t>Pondicherry</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>Pondicherry</t>
-        </is>
-      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>02:05</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>03:25</t>
+          <t>06:28</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>trip_b96c804b5a1862f4</t>
+          <t>trip_4bad1d9396432966</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>log_d9a60a2a978dcd</t>
+          <t>log_b9357b65d50b28</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>144.251</v>
+        <v>128.889</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0</v>
@@ -3562,20 +3562,20 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>maduravoyal &gt; madiwala</t>
+          <t>chennai &gt; pondicherry</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>46276.97569444445</v>
+        <v>46220.31736111111</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>46277.23888888889</v>
+        <v>46220.48819444444</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>39.933</v>
+        <v>457</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>13.967</v>
+        <v>703</v>
       </c>
       <c r="K32" s="2" t="b">
         <v>0</v>
@@ -3584,7 +3584,7 @@
         <v>1</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>144.251</v>
+        <v>128.889</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -3593,59 +3593,59 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+          <t>chennai_to_pondi_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>11-09-2026\maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+          <t>17-07-2026\chennai_to_pondi_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="R32" s="2" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>46276</v>
+        <v>46220</v>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>Maduravoyal</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>Madiwala</t>
+          <t>Pondicherry</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23:25:00</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>05:44 (+1 day)</t>
+          <t>11:43</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>trip_23c8e313df2d9321</t>
+          <t>trip_af094e2aa84e3fd8</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>log_e7bca7591f2c6a</t>
+          <t>log_baab598cc0961a</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>144.728</v>
+        <v>144.673</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>0</v>
@@ -3655,20 +3655,20 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>silkboard &gt; maduravoyal</t>
+          <t>madiwala &gt; maduravoyal</t>
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>46270.01388888889</v>
+        <v>46277.96597222222</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>46270.25138888889</v>
+        <v>46278.19722222222</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>11.517</v>
+        <v>2.083</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8.083</v>
+        <v>21.45</v>
       </c>
       <c r="K33" s="2" t="b">
         <v>0</v>
@@ -3677,7 +3677,7 @@
         <v>1</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>144.728</v>
+        <v>144.673</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -3686,28 +3686,28 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+          <t>madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>05-09-2026\silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+          <t>12-09-2026\madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="R33" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="S33" s="5" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>Silk Board</t>
+          <t>Madiwala</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -3717,28 +3717,28 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>00:20:00</t>
+          <t>23:11:00</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>06:02 (+1 day)</t>
+          <t>04:44 (+1 day)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>trip_4c268f26d8d1823c</t>
+          <t>trip_07f23f699f56d574</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>log_f2ee838b3c9667</t>
+          <t>log_bcde7a9312a413</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>125.818</v>
+        <v>144.669</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>0</v>
@@ -3748,20 +3748,20 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>chennai &gt; pondicherry</t>
+          <t>silkboard &gt; maduravoyal</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>46218.47083333333</v>
+        <v>46223.49583333333</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>46218.66319444445</v>
+        <v>46223.74861111111</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>678</v>
+        <v>6</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>703.083</v>
+        <v>17.8</v>
       </c>
       <c r="K34" s="2" t="b">
         <v>0</v>
@@ -3770,7 +3770,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>125.818</v>
+        <v>144.669</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -3779,141 +3779,699 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>chennai_to_pondi_diesel_INTERCITY.xlsx</t>
+          <t>silkboard_to_maduravoyal_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>15-07-2026\chennai_to_pondi_diesel_INTERCITY.xlsx</t>
+          <t>20-07-2026\silkboard_to_maduravoyal_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="R34" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="S34" s="5" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Silk Board</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Maduravoyal</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>03:55</t>
+          <t>05:58</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>trip_e2f68314e0d730f0</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>log_cf162b454c984b</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>144.974</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>pondicherry &gt; chennai</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>46291.6</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>46291.78958333333</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="K35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>144.974</v>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>pondicherry_to_chennai_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>26-09-2026\pondicherry_to_chennai_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="S35" s="5" t="n">
+        <v>46291</v>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>Pondicherry</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>14:24:00</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>18:57:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>trip_6088a97c1b8893d7</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>log_d0035ab1754ec5</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>127.749</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>pondicherry &gt; chennai</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>46219.6875</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>46219.86805555555</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>712.1</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>530</v>
+      </c>
+      <c r="K36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>127.749</v>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>pondi_to_chennai_diesel_INTERCITY.xlsx</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>16-07-2026\pondi_to_chennai_diesel_INTERCITY.xlsx</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S36" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>Pondicherry</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>trip_e27cf5973e77ff0f</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>log_d48233712f4cfc</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>125.654</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>chennai &gt; pondicherry</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>46220.48194444444</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>46220.64236111111</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>694</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>698.933</v>
+      </c>
+      <c r="K37" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>125.654</v>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>chennai_to_pondi_diesel_INTERCITY.xlsx</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>17-07-2026\chennai_to_pondi_diesel_INTERCITY.xlsx</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S37" s="5" t="n">
+        <v>46220</v>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>Pondicherry</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>trip_b96c804b5a1862f4</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>log_d9a60a2a978dcd</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>144.251</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>maduravoyal &gt; madiwala</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>46276.97569444445</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>46277.23888888889</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>39.933</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>13.967</v>
+      </c>
+      <c r="K38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>144.251</v>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>11-09-2026\maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="S38" s="5" t="n">
+        <v>46276</v>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>Maduravoyal</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>Madiwala</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>23:25:00</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>05:44 (+1 day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>trip_23c8e313df2d9321</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>log_e7bca7591f2c6a</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>144.728</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>silkboard &gt; maduravoyal</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>46270.01388888889</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>46270.25138888889</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>11.517</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>8.083</v>
+      </c>
+      <c r="K39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>144.728</v>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>05-09-2026\silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="S39" s="5" t="n">
+        <v>46270</v>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>Silk Board</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>Maduravoyal</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>00:20:00</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>06:02 (+1 day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>trip_4c268f26d8d1823c</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>log_f2ee838b3c9667</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>125.818</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>chennai &gt; pondicherry</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>46218.47083333333</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>46218.66319444445</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>678</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>703.083</v>
+      </c>
+      <c r="K40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>125.818</v>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>chennai_to_pondi_diesel_INTERCITY.xlsx</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>15-07-2026\chennai_to_pondi_diesel_INTERCITY.xlsx</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S40" s="5" t="n">
+        <v>46218</v>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>Pondicherry</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>03:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
           <t>trip_c8bb5b5f79a60226</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>log_fabc09242a326c</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
+      <c r="C41" s="2" t="n">
         <v>138.211</v>
       </c>
-      <c r="D35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="D41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>pondicherry &gt; chennai</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>46223.17708333334</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>46223.34166666667</v>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="I41" s="2" t="n">
         <v>465</v>
       </c>
-      <c r="J35" s="2" t="n">
+      <c r="J41" s="2" t="n">
         <v>23.783</v>
       </c>
-      <c r="K35" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M35" s="2" t="n">
+      <c r="K41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" s="2" t="n">
         <v>138.211</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
+      <c r="O41" s="3" t="inlineStr">
         <is>
           <t>pondi_to_chennai_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
-      <c r="P35" s="3" t="inlineStr">
+      <c r="P41" s="3" t="inlineStr">
         <is>
           <t>20-07-2026\pondi_to_chennai_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>ICE</t>
         </is>
       </c>
-      <c r="R35" s="2" t="n">
+      <c r="R41" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="S35" s="5" t="n">
+      <c r="S41" s="5" t="n">
         <v>46223</v>
       </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="T41" s="2" t="inlineStr">
         <is>
           <t>Pondicherry</t>
         </is>
       </c>
-      <c r="U35" s="2" t="inlineStr">
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="W35" s="2" t="inlineStr">
+      <c r="W41" s="2" t="inlineStr">
         <is>
           <t>20:12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W35"/>
+  <autoFilter ref="A1:W41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3924,7 +4482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN35"/>
+  <dimension ref="A1:BN41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -10672,7 +11230,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>verified_ba92432e63144128</t>
+          <t>verified_3999a99ea92a6128</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -10700,7 +11258,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>trip_94455ac95468fa9e</t>
+          <t>trip_af094e2aa84e3fd8</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -10730,7 +11288,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 22:33:23</t>
+          <t>2026-09-12 23:13:05</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10739,10 +11297,10 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>12.92092</v>
+        <v>12.91943</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>77.62052</v>
+        <v>77.62147</v>
       </c>
       <c r="Q28" s="2" t="n">
         <v>13.07773</v>
@@ -10751,10 +11309,10 @@
         <v>80.14538</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>328.955</v>
+        <v>328.617</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
@@ -10820,7 +11378,7 @@
       <c r="AJ28" s="2" t="inlineStr"/>
       <c r="AK28" s="3" t="inlineStr"/>
       <c r="AL28" s="2" t="n">
-        <v>144.18</v>
+        <v>144.673</v>
       </c>
       <c r="AM28" s="2" t="n">
         <v>0</v>
@@ -10842,7 +11400,7 @@
         </is>
       </c>
       <c r="AR28" s="2" t="n">
-        <v>144.18</v>
+        <v>144.673</v>
       </c>
       <c r="AS28" s="2" t="inlineStr">
         <is>
@@ -10885,25 +11443,25 @@
         <v>70</v>
       </c>
       <c r="BE28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF28" s="2" t="n">
         <v>59</v>
       </c>
       <c r="BG28" s="2" t="n">
-        <v>39.7</v>
+        <v>0</v>
       </c>
       <c r="BH28" s="2" t="n">
         <v>22.617</v>
       </c>
       <c r="BI28" s="2" t="n">
-        <v>0.33794</v>
+        <v>0</v>
       </c>
       <c r="BJ28" s="2" t="n">
         <v>2.85894</v>
       </c>
       <c r="BK28" s="2" t="n">
-        <v>328.955194</v>
+        <v>328.617254</v>
       </c>
       <c r="BL28" s="2" t="n">
         <v>0</v>
@@ -11306,11 +11864,7 @@
       <c r="AH30" s="2" t="inlineStr"/>
       <c r="AI30" s="2" t="inlineStr"/>
       <c r="AJ30" s="2" t="inlineStr"/>
-      <c r="AK30" s="3" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
+      <c r="AK30" s="3" t="inlineStr"/>
       <c r="AL30" s="2" t="n">
         <v>144.958</v>
       </c>
@@ -11656,7 +12210,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>verified_6976a3c9c0dc9943</t>
+          <t>verified_39969069fa8862e0</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -11742,7 +12296,7 @@
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>log_862cda94cb0701</t>
+          <t>log_95966633d8fcec</t>
         </is>
       </c>
       <c r="V32" s="2" t="n">
@@ -11780,7 +12334,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>18:17 (+1 day)</t>
+          <t>18:17:00</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr"/>
@@ -12400,7 +12954,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>verified_2ef63d7709cb5e84</t>
+          <t>verified_d562523e804f885b</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -12428,131 +12982,127 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>trip_0e87f413df33f4c0</t>
+          <t>trip_42cecab159306ac4</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>pondicherry_to_chennai_ev_intercity.xlsx</t>
+          <t>chennai_to_pondicherry_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>26-09-2026\pondicherry_to_chennai_ev_intercity.xlsx</t>
+          <t>25-09-2026\chennai_to_pondicherry_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Cleaned\26-09-2026\pondicherry_to_chennai_ev_intercity.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Cleaned\25-09-2026\chennai_to_pondicherry_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>pondicherry_to_chennai_intercity</t>
+          <t>chennai_to_pondicherry_intercity</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:24:58</t>
+          <t>2026-09-25 14:27:10</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 18:57:55</t>
+          <t>2026-09-25 19:56:45</t>
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>11.93305</v>
+        <v>13.06988</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>79.80752</v>
+        <v>80.20525000000001</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>13.0535</v>
+        <v>11.93708</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>80.21156999999999</v>
+        <v>79.81917</v>
       </c>
       <c r="S35" s="2" t="n">
-        <v>217.102</v>
+        <v>155.148</v>
       </c>
       <c r="T35" s="2" t="n">
-        <v>2675</v>
+        <v>957</v>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>log_cf162b454c984b</t>
+          <t>log_7a83e37e272f23</t>
         </is>
       </c>
       <c r="V35" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>AP39 WH5781</t>
+          <t>TN 68S 0922</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>Pondicherry to Chennai</t>
+          <t>Chennai to Pondicherry</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>Pondicherry</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>14:26:00</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18:57:00</t>
+          <t>19:13:00</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr"/>
       <c r="AE35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:24:00</t>
+          <t>2026-09-25 14:26:00</t>
         </is>
       </c>
       <c r="AF35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 18:57:00</t>
+          <t>2026-09-25 19:13:00</t>
         </is>
       </c>
       <c r="AG35" s="2" t="inlineStr">
         <is>
-          <t>IIT-3</t>
+          <t>IIT-1</t>
         </is>
       </c>
       <c r="AH35" s="2" t="inlineStr"/>
       <c r="AI35" s="2" t="inlineStr"/>
       <c r="AJ35" s="2" t="inlineStr"/>
-      <c r="AK35" s="3" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
+      <c r="AK35" s="3" t="inlineStr"/>
       <c r="AL35" s="2" t="n">
-        <v>144.974</v>
+        <v>144.376</v>
       </c>
       <c r="AM35" s="2" t="n">
         <v>0</v>
@@ -12562,7 +13112,7 @@
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>pondicherry &gt; chennai</t>
+          <t>chennai &gt; pondicherry</t>
         </is>
       </c>
       <c r="AP35" s="2" t="b">
@@ -12574,68 +13124,68 @@
         </is>
       </c>
       <c r="AR35" s="2" t="n">
-        <v>144.974</v>
+        <v>144.376</v>
       </c>
       <c r="AS35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:24:58</t>
+          <t>2026-09-25 14:27:10</t>
         </is>
       </c>
       <c r="AT35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 18:55:10</t>
+          <t>2026-09-25 19:12:44</t>
         </is>
       </c>
       <c r="AU35" s="2" t="n">
-        <v>11.93305</v>
+        <v>13.06988</v>
       </c>
       <c r="AV35" s="2" t="n">
-        <v>79.80752</v>
+        <v>80.20525000000001</v>
       </c>
       <c r="AW35" s="2" t="n">
-        <v>13.05348</v>
+        <v>11.93228</v>
       </c>
       <c r="AX35" s="2" t="n">
-        <v>80.21163</v>
+        <v>79.8077</v>
       </c>
       <c r="AY35" s="2" t="n">
-        <v>270.2</v>
+        <v>285.567</v>
       </c>
       <c r="AZ35" s="2" t="n">
-        <v>217.094982</v>
+        <v>153.527156</v>
       </c>
       <c r="BA35" s="2" t="n">
-        <v>132.084613</v>
+        <v>133.654866</v>
       </c>
       <c r="BB35" s="2" t="n">
-        <v>2672</v>
+        <v>887</v>
       </c>
       <c r="BC35" s="2" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="BD35" s="2" t="n">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="BE35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="BF35" s="2" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="BG35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="BH35" s="2" t="n">
-        <v>2.75</v>
+        <v>44.017</v>
       </c>
       <c r="BI35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="BJ35" s="2" t="n">
-        <v>0.006938</v>
+        <v>1.621253</v>
       </c>
       <c r="BK35" s="2" t="n">
-        <v>217.10192</v>
+        <v>155.148409</v>
       </c>
       <c r="BL35" s="2" t="n">
         <v>0</v>
@@ -12645,8 +13195,1484 @@
         <v>1</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>verified_00f28ce0faa56f73</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>READY_FOR_PAIRING</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Full telemetry supports the logged start/end window</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>LOG_ANCHORED</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>trip_e2f68314e0d730f0</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>pondicherry_to_chennai_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>26-09-2026\pondicherry_to_chennai_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Cleaned\26-09-2026\pondicherry_to_chennai_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>pondicherry_to_chennai_intercity</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 14:24:58</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 18:57:55</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>11.93305</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>79.80752</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>13.0535</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>80.21156999999999</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>152.544</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>2675</v>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>log_cf162b454c984b</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>AP39 WH5781</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>Pondicherry</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>14:24:00</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>18:57:00</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 14:24:00</t>
+        </is>
+      </c>
+      <c r="AF36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 18:57:00</t>
+        </is>
+      </c>
+      <c r="AG36" s="2" t="inlineStr">
+        <is>
+          <t>IIT-3</t>
+        </is>
+      </c>
+      <c r="AH36" s="2" t="inlineStr"/>
+      <c r="AI36" s="2" t="inlineStr"/>
+      <c r="AJ36" s="2" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="AL36" s="2" t="n">
+        <v>144.974</v>
+      </c>
+      <c r="AM36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>pondicherry &gt; chennai</t>
+        </is>
+      </c>
+      <c r="AP36" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ36" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AR36" s="2" t="n">
+        <v>144.974</v>
+      </c>
+      <c r="AS36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 14:24:58</t>
+        </is>
+      </c>
+      <c r="AT36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 18:55:10</t>
+        </is>
+      </c>
+      <c r="AU36" s="2" t="n">
+        <v>11.93305</v>
+      </c>
+      <c r="AV36" s="2" t="n">
+        <v>79.80752</v>
+      </c>
+      <c r="AW36" s="2" t="n">
+        <v>13.05348</v>
+      </c>
+      <c r="AX36" s="2" t="n">
+        <v>80.21163</v>
+      </c>
+      <c r="AY36" s="2" t="n">
+        <v>270.2</v>
+      </c>
+      <c r="AZ36" s="2" t="n">
+        <v>152.537404</v>
+      </c>
+      <c r="BA36" s="2" t="n">
+        <v>132.084613</v>
+      </c>
+      <c r="BB36" s="2" t="n">
+        <v>2672</v>
+      </c>
+      <c r="BC36" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="BD36" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="BE36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BI36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ36" s="2" t="n">
+        <v>0.006938</v>
+      </c>
+      <c r="BK36" s="2" t="n">
+        <v>152.544342</v>
+      </c>
+      <c r="BL36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM36" s="2" t="inlineStr"/>
+      <c r="BN36" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>verified_a308cae97aa5a528</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>READY_FOR_PAIRING</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Full telemetry supports the logged start/end window</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>LOG_ANCHORED</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>trip_efd3430444a3f8eb</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>pondicherry_to_chennai_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>26-09-2026\pondicherry_to_chennai_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Cleaned\26-09-2026\pondicherry_to_chennai_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>pondicherry_to_chennai_intercity</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 16:11:58</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 21:18:23</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>11.93333</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>79.80748</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>13.0758</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>80.19855</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>155.992</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>973</v>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>log_aba8d06ef2bf51</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>TN50BT0800</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>Pondicherry</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>21:10:00</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 16:15:00</t>
+        </is>
+      </c>
+      <c r="AF37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 21:10:00</t>
+        </is>
+      </c>
+      <c r="AG37" s="2" t="inlineStr">
+        <is>
+          <t>IIT-2</t>
+        </is>
+      </c>
+      <c r="AH37" s="2" t="inlineStr"/>
+      <c r="AI37" s="2" t="inlineStr"/>
+      <c r="AJ37" s="2" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="2" t="n">
+        <v>144.841</v>
+      </c>
+      <c r="AM37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>pondicherry &gt; chennai</t>
+        </is>
+      </c>
+      <c r="AP37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ37" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AR37" s="2" t="n">
+        <v>144.841</v>
+      </c>
+      <c r="AS37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 16:16:08</t>
+        </is>
+      </c>
+      <c r="AT37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 21:07:53</t>
+        </is>
+      </c>
+      <c r="AU37" s="2" t="n">
+        <v>11.94062</v>
+      </c>
+      <c r="AV37" s="2" t="n">
+        <v>79.80826999999999</v>
+      </c>
+      <c r="AW37" s="2" t="n">
+        <v>13.0689</v>
+      </c>
+      <c r="AX37" s="2" t="n">
+        <v>80.2062</v>
+      </c>
+      <c r="AY37" s="2" t="n">
+        <v>291.75</v>
+      </c>
+      <c r="AZ37" s="2" t="n">
+        <v>154.029182</v>
+      </c>
+      <c r="BA37" s="2" t="n">
+        <v>132.68769</v>
+      </c>
+      <c r="BB37" s="2" t="n">
+        <v>954</v>
+      </c>
+      <c r="BC37" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="BD37" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="BE37" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF37" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG37" s="2" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="BH37" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BI37" s="2" t="n">
+        <v>0.81811</v>
+      </c>
+      <c r="BJ37" s="2" t="n">
+        <v>1.144213</v>
+      </c>
+      <c r="BK37" s="2" t="n">
+        <v>155.991505</v>
+      </c>
+      <c r="BL37" s="2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM37" s="2" t="inlineStr"/>
+      <c r="BN37" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>verified_f410ae27b0a3a36e</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>READY_FOR_PAIRING</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Full telemetry supports the logged start/end window</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>LOG_ANCHORED</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>trip_13cc5a5f3743a171</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>02-10-2026\maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Cleaned\02-10-2026\maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_intercity</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 22:30:08</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:20:03</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>13.0776</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>80.14534999999999</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>12.96495</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>77.59851999999999</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>338.048</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>1342</v>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>log_12f913058881aa</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>TN95M6802</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>Maduravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>Maduravoyal</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>Madiwala</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>23:29:00</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>04:52 (+1 day)</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:29:00</t>
+        </is>
+      </c>
+      <c r="AF38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 04:52:00</t>
+        </is>
+      </c>
+      <c r="AG38" s="2" t="inlineStr">
+        <is>
+          <t>IIT-1</t>
+        </is>
+      </c>
+      <c r="AH38" s="2" t="inlineStr"/>
+      <c r="AI38" s="2" t="inlineStr"/>
+      <c r="AJ38" s="2" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz 16T</t>
+        </is>
+      </c>
+      <c r="AL38" s="2" t="n">
+        <v>143.793</v>
+      </c>
+      <c r="AM38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>maduravoyal &gt; madiwala</t>
+        </is>
+      </c>
+      <c r="AP38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ38" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AR38" s="2" t="n">
+        <v>143.793</v>
+      </c>
+      <c r="AS38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:29:56</t>
+        </is>
+      </c>
+      <c r="AT38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 04:50:08</t>
+        </is>
+      </c>
+      <c r="AU38" s="2" t="n">
+        <v>13.06115</v>
+      </c>
+      <c r="AV38" s="2" t="n">
+        <v>80.16342</v>
+      </c>
+      <c r="AW38" s="2" t="n">
+        <v>12.91982</v>
+      </c>
+      <c r="AX38" s="2" t="n">
+        <v>77.62087</v>
+      </c>
+      <c r="AY38" s="2" t="n">
+        <v>320.2</v>
+      </c>
+      <c r="AZ38" s="2" t="n">
+        <v>326.185417</v>
+      </c>
+      <c r="BA38" s="2" t="n">
+        <v>275.930196</v>
+      </c>
+      <c r="BB38" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="BC38" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="BD38" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="BE38" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="BF38" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="BG38" s="2" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="BH38" s="2" t="n">
+        <v>29.917</v>
+      </c>
+      <c r="BI38" s="2" t="n">
+        <v>4.577086</v>
+      </c>
+      <c r="BJ38" s="2" t="n">
+        <v>7.28586</v>
+      </c>
+      <c r="BK38" s="2" t="n">
+        <v>338.048364</v>
+      </c>
+      <c r="BL38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM38" s="2" t="inlineStr"/>
+      <c r="BN38" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>verified_4688f07d3763df8b</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>READY_FOR_PAIRING</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Full telemetry supports the logged start/end window</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>LOG_ANCHORED</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>trip_c878323a9bdf7813</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>02-10-2026\maduravoyal_to_madiwala_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Cleaned\02-10-2026\maduravoyal_to_madiwala_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_intercity</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:08:47</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:29:54</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>13.06127</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>80.16488</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>12.95547</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>77.59188</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>332.343</v>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>3631</v>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>log_4058b1efc303e6</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>TN14AR3998</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>Maduravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>Maduravoyal</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>Madiwala</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>23:08:00</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>05:07 (+1 day)</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:08:00</t>
+        </is>
+      </c>
+      <c r="AF39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:07:00</t>
+        </is>
+      </c>
+      <c r="AG39" s="2" t="inlineStr">
+        <is>
+          <t>IIT-3</t>
+        </is>
+      </c>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
+      <c r="AJ39" s="2" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="2" t="n">
+        <v>144.671</v>
+      </c>
+      <c r="AM39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>maduravoyal &gt; madiwala</t>
+        </is>
+      </c>
+      <c r="AP39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ39" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AR39" s="2" t="n">
+        <v>144.671</v>
+      </c>
+      <c r="AS39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:08:47</t>
+        </is>
+      </c>
+      <c r="AT39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:06:58</t>
+        </is>
+      </c>
+      <c r="AU39" s="2" t="n">
+        <v>13.06127</v>
+      </c>
+      <c r="AV39" s="2" t="n">
+        <v>80.16488</v>
+      </c>
+      <c r="AW39" s="2" t="n">
+        <v>12.91193</v>
+      </c>
+      <c r="AX39" s="2" t="n">
+        <v>77.62588</v>
+      </c>
+      <c r="AY39" s="2" t="n">
+        <v>358.183</v>
+      </c>
+      <c r="AZ39" s="2" t="n">
+        <v>325.627286</v>
+      </c>
+      <c r="BA39" s="2" t="n">
+        <v>275.602705</v>
+      </c>
+      <c r="BB39" s="2" t="n">
+        <v>3465</v>
+      </c>
+      <c r="BC39" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="BD39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="BG39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" s="2" t="n">
+        <v>22.933</v>
+      </c>
+      <c r="BI39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ39" s="2" t="n">
+        <v>6.715322</v>
+      </c>
+      <c r="BK39" s="2" t="n">
+        <v>332.342608</v>
+      </c>
+      <c r="BL39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM39" s="2" t="inlineStr"/>
+      <c r="BN39" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>verified_9d60b01a5d7ad63f</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>READY_FOR_PAIRING</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Full telemetry supports the logged start/end window</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>LOG_ANCHORED</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>trip_f1948b8b1dd14218</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>03-10-2026\madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Cleaned\03-10-2026\madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>madiwala_to_maduravoyal_intercity</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 22:00:02</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 04:11:15</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>12.92075</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>77.6206</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>13.07758</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>80.14537</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>328.193</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>1273</v>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>log_117f2e1c26ca9e</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>TN95M6802</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>Madiwala to Maduravoyal</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>Madiwala</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>Maduravoyal</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>03:53 (+1 day)</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 22:00:00</t>
+        </is>
+      </c>
+      <c r="AF40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 03:53:00</t>
+        </is>
+      </c>
+      <c r="AG40" s="2" t="inlineStr">
+        <is>
+          <t>IIT-1</t>
+        </is>
+      </c>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz 16T</t>
+        </is>
+      </c>
+      <c r="AL40" s="2" t="n">
+        <v>144.746</v>
+      </c>
+      <c r="AM40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>madiwala &gt; maduravoyal</t>
+        </is>
+      </c>
+      <c r="AP40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ40" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AR40" s="2" t="n">
+        <v>144.746</v>
+      </c>
+      <c r="AS40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 22:00:02</t>
+        </is>
+      </c>
+      <c r="AT40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 03:52:46</t>
+        </is>
+      </c>
+      <c r="AU40" s="2" t="n">
+        <v>12.92075</v>
+      </c>
+      <c r="AV40" s="2" t="n">
+        <v>77.6206</v>
+      </c>
+      <c r="AW40" s="2" t="n">
+        <v>13.06197</v>
+      </c>
+      <c r="AX40" s="2" t="n">
+        <v>80.14597999999999</v>
+      </c>
+      <c r="AY40" s="2" t="n">
+        <v>352.733</v>
+      </c>
+      <c r="AZ40" s="2" t="n">
+        <v>325.024121</v>
+      </c>
+      <c r="BA40" s="2" t="n">
+        <v>274.071239</v>
+      </c>
+      <c r="BB40" s="2" t="n">
+        <v>1232</v>
+      </c>
+      <c r="BC40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD40" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="BG40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" s="2" t="n">
+        <v>18.483</v>
+      </c>
+      <c r="BI40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ40" s="2" t="n">
+        <v>3.16873</v>
+      </c>
+      <c r="BK40" s="2" t="n">
+        <v>328.192851</v>
+      </c>
+      <c r="BL40" s="2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM40" s="2" t="inlineStr"/>
+      <c r="BN40" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>verified_7b146c00c20ce367</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>READY_FOR_PAIRING</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Full telemetry supports the logged start/end window</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>LOG_ANCHORED</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>trip_25c5675923bf855a</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>03-10-2026\madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Cleaned\03-10-2026\madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>madiwala_to_maduravoyal_intercity</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 21:29:04</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:00:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>12.95338</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>77.59275</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>13.06195</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>80.16562</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>332.625</v>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>4237</v>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>log_1fa2f4469203bc</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>TN14V9606</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>Madiwala to Maduravoyal</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>Madiwala</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>Maduravoyal</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>05:00 (+1 day)</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 21:30:00</t>
+        </is>
+      </c>
+      <c r="AF41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:00:00</t>
+        </is>
+      </c>
+      <c r="AG41" s="2" t="inlineStr">
+        <is>
+          <t>IIT-3</t>
+        </is>
+      </c>
+      <c r="AH41" s="2" t="inlineStr"/>
+      <c r="AI41" s="2" t="inlineStr"/>
+      <c r="AJ41" s="2" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="2" t="n">
+        <v>144.975</v>
+      </c>
+      <c r="AM41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>madiwala &gt; maduravoyal</t>
+        </is>
+      </c>
+      <c r="AP41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ41" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AR41" s="2" t="n">
+        <v>144.975</v>
+      </c>
+      <c r="AS41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 21:34:00</t>
+        </is>
+      </c>
+      <c r="AT41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 04:59:52</t>
+        </is>
+      </c>
+      <c r="AU41" s="2" t="n">
+        <v>12.95298</v>
+      </c>
+      <c r="AV41" s="2" t="n">
+        <v>77.59335</v>
+      </c>
+      <c r="AW41" s="2" t="n">
+        <v>13.06138</v>
+      </c>
+      <c r="AX41" s="2" t="n">
+        <v>80.16397000000001</v>
+      </c>
+      <c r="AY41" s="2" t="n">
+        <v>445.867</v>
+      </c>
+      <c r="AZ41" s="2" t="n">
+        <v>332.352855</v>
+      </c>
+      <c r="BA41" s="2" t="n">
+        <v>278.765651</v>
+      </c>
+      <c r="BB41" s="2" t="n">
+        <v>4230</v>
+      </c>
+      <c r="BC41" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="BD41" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF41" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG41" s="2" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="BH41" s="2" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="BI41" s="2" t="n">
+        <v>0.078777</v>
+      </c>
+      <c r="BJ41" s="2" t="n">
+        <v>0.193246</v>
+      </c>
+      <c r="BK41" s="2" t="n">
+        <v>332.624878</v>
+      </c>
+      <c r="BL41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM41" s="2" t="inlineStr"/>
+      <c r="BN41" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BN35"/>
+  <autoFilter ref="A1:BN41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
